--- a/P012-excavator-split_data_files/28_05_2017_yared girmaw-excavator_records_part_6.xlsx
+++ b/P012-excavator-split_data_files/28_05_2017_yared girmaw-excavator_records_part_6.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="excavator" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="mpdm" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="daily_variables" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="excavator" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mpdm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_variables" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z81"/>
+  <dimension ref="A1:Z111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.875" customWidth="1" min="1" max="1"/>
@@ -5907,6 +5907,1296 @@
       <c r="X81" s="10" t="n"/>
       <c r="Y81" s="10" t="n"/>
       <c r="Z81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="E82" t="n">
+        <v>505</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L82" t="n">
+        <v>120</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R82" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="E83" t="n">
+        <v>505</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L83" t="n">
+        <v>120</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R83" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="E84" t="n">
+        <v>505</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L84" t="n">
+        <v>120</v>
+      </c>
+      <c r="M84" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R84" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="E85" t="n">
+        <v>505</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L85" t="n">
+        <v>120</v>
+      </c>
+      <c r="M85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R85" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="E86" t="n">
+        <v>505</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L86" t="n">
+        <v>120</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R86" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="E87" t="n">
+        <v>505</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L87" t="n">
+        <v>120</v>
+      </c>
+      <c r="M87" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R87" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="E88" t="n">
+        <v>505</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L88" t="n">
+        <v>120</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R88" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="E89" t="n">
+        <v>505</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L89" t="n">
+        <v>120</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R89" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="E90" t="n">
+        <v>505</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L90" t="n">
+        <v>120</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R90" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="E91" t="n">
+        <v>505</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L91" t="n">
+        <v>120</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R91" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="E92" t="n">
+        <v>505</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L92" t="n">
+        <v>120</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R92" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="E93" t="n">
+        <v>505</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L93" t="n">
+        <v>120</v>
+      </c>
+      <c r="M93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R93" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="E94" t="n">
+        <v>505</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L94" t="n">
+        <v>120</v>
+      </c>
+      <c r="M94" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R94" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="E95" t="n">
+        <v>505</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L95" t="n">
+        <v>120</v>
+      </c>
+      <c r="M95" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R95" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="E96" t="n">
+        <v>505</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L96" t="n">
+        <v>120</v>
+      </c>
+      <c r="M96" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R96" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="E97" t="n">
+        <v>505</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L97" t="n">
+        <v>120</v>
+      </c>
+      <c r="M97" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R97" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="E98" t="n">
+        <v>505</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L98" t="n">
+        <v>120</v>
+      </c>
+      <c r="M98" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R98" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="E99" t="n">
+        <v>505</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L99" t="n">
+        <v>120</v>
+      </c>
+      <c r="M99" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R99" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="E100" t="n">
+        <v>505</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L100" t="n">
+        <v>120</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R100" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="E101" t="n">
+        <v>505</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L101" t="n">
+        <v>120</v>
+      </c>
+      <c r="M101" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R101" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="E102" t="n">
+        <v>505</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L102" t="n">
+        <v>120</v>
+      </c>
+      <c r="M102" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R102" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="E103" t="n">
+        <v>505</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L103" t="n">
+        <v>120</v>
+      </c>
+      <c r="M103" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R103" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="E104" t="n">
+        <v>505</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L104" t="n">
+        <v>120</v>
+      </c>
+      <c r="M104" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R104" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="E105" t="n">
+        <v>505</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L105" t="n">
+        <v>120</v>
+      </c>
+      <c r="M105" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R105" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="E106" t="n">
+        <v>505</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L106" t="n">
+        <v>120</v>
+      </c>
+      <c r="M106" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R106" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="E107" t="n">
+        <v>505</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L107" t="n">
+        <v>120</v>
+      </c>
+      <c r="M107" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R107" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="E108" t="n">
+        <v>505</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L108" t="n">
+        <v>120</v>
+      </c>
+      <c r="M108" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R108" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="E109" t="n">
+        <v>505</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L109" t="n">
+        <v>120</v>
+      </c>
+      <c r="M109" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R109" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="E110" t="n">
+        <v>505</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L110" t="n">
+        <v>120</v>
+      </c>
+      <c r="M110" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R110" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="E111" t="n">
+        <v>505</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1/12 foreman,1 operator, 1helper</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>soft rock excavation using hydraulic exvavator</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L111" t="n">
+        <v>120</v>
+      </c>
+      <c r="M111" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R111" t="n">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -9974,7 +11264,7 @@
       </c>
       <c r="H21" s="70" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I21" s="68" t="n"/>

--- a/P012-excavator-split_data_files/28_05_2017_yared girmaw-excavator_records_part_6.xlsx
+++ b/P012-excavator-split_data_files/28_05_2017_yared girmaw-excavator_records_part_6.xlsx
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z111"/>
+  <dimension ref="A1:Z81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.875" customWidth="1" min="1" max="1"/>
@@ -1628,10 +1628,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n"/>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>28-05-2017</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Yared Girmaw</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>2</v>
+      </c>
       <c r="E7" s="19" t="n">
         <v>501</v>
       </c>
@@ -5907,1296 +5919,6 @@
       <c r="X81" s="10" t="n"/>
       <c r="Y81" s="10" t="n"/>
       <c r="Z81" s="10" t="n"/>
-    </row>
-    <row r="82">
-      <c r="E82" t="n">
-        <v>505</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K82" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L82" t="n">
-        <v>120</v>
-      </c>
-      <c r="M82" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R82" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="E83" t="n">
-        <v>505</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K83" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L83" t="n">
-        <v>120</v>
-      </c>
-      <c r="M83" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R83" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="E84" t="n">
-        <v>505</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K84" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L84" t="n">
-        <v>120</v>
-      </c>
-      <c r="M84" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R84" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="E85" t="n">
-        <v>505</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L85" t="n">
-        <v>120</v>
-      </c>
-      <c r="M85" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R85" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="E86" t="n">
-        <v>505</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L86" t="n">
-        <v>120</v>
-      </c>
-      <c r="M86" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N86" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R86" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="E87" t="n">
-        <v>505</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L87" t="n">
-        <v>120</v>
-      </c>
-      <c r="M87" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R87" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="E88" t="n">
-        <v>505</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L88" t="n">
-        <v>120</v>
-      </c>
-      <c r="M88" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R88" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="E89" t="n">
-        <v>505</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K89" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L89" t="n">
-        <v>120</v>
-      </c>
-      <c r="M89" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R89" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="E90" t="n">
-        <v>505</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K90" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L90" t="n">
-        <v>120</v>
-      </c>
-      <c r="M90" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R90" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="E91" t="n">
-        <v>505</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L91" t="n">
-        <v>120</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R91" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="E92" t="n">
-        <v>505</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K92" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L92" t="n">
-        <v>120</v>
-      </c>
-      <c r="M92" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R92" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="E93" t="n">
-        <v>505</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L93" t="n">
-        <v>120</v>
-      </c>
-      <c r="M93" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R93" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="E94" t="n">
-        <v>505</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L94" t="n">
-        <v>120</v>
-      </c>
-      <c r="M94" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R94" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="E95" t="n">
-        <v>505</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L95" t="n">
-        <v>120</v>
-      </c>
-      <c r="M95" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N95" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R95" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="E96" t="n">
-        <v>505</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L96" t="n">
-        <v>120</v>
-      </c>
-      <c r="M96" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R96" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="E97" t="n">
-        <v>505</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K97" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L97" t="n">
-        <v>120</v>
-      </c>
-      <c r="M97" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N97" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R97" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="E98" t="n">
-        <v>505</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K98" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L98" t="n">
-        <v>120</v>
-      </c>
-      <c r="M98" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R98" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="E99" t="n">
-        <v>505</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K99" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L99" t="n">
-        <v>120</v>
-      </c>
-      <c r="M99" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N99" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R99" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="E100" t="n">
-        <v>505</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L100" t="n">
-        <v>120</v>
-      </c>
-      <c r="M100" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R100" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="E101" t="n">
-        <v>505</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L101" t="n">
-        <v>120</v>
-      </c>
-      <c r="M101" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R101" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="E102" t="n">
-        <v>505</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L102" t="n">
-        <v>120</v>
-      </c>
-      <c r="M102" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R102" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="E103" t="n">
-        <v>505</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K103" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L103" t="n">
-        <v>120</v>
-      </c>
-      <c r="M103" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N103" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R103" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="E104" t="n">
-        <v>505</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K104" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L104" t="n">
-        <v>120</v>
-      </c>
-      <c r="M104" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N104" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R104" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="E105" t="n">
-        <v>505</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K105" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L105" t="n">
-        <v>120</v>
-      </c>
-      <c r="M105" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R105" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="E106" t="n">
-        <v>505</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K106" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L106" t="n">
-        <v>120</v>
-      </c>
-      <c r="M106" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R106" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="E107" t="n">
-        <v>505</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K107" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L107" t="n">
-        <v>120</v>
-      </c>
-      <c r="M107" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R107" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="E108" t="n">
-        <v>505</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K108" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L108" t="n">
-        <v>120</v>
-      </c>
-      <c r="M108" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R108" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="E109" t="n">
-        <v>505</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K109" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L109" t="n">
-        <v>120</v>
-      </c>
-      <c r="M109" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N109" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R109" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="E110" t="n">
-        <v>505</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K110" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L110" t="n">
-        <v>120</v>
-      </c>
-      <c r="M110" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N110" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R110" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="E111" t="n">
-        <v>505</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>1/12 foreman,1 operator, 1helper</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>soft rock excavation using hydraulic exvavator</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>clay and gravel</t>
-        </is>
-      </c>
-      <c r="K111" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L111" t="n">
-        <v>120</v>
-      </c>
-      <c r="M111" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N111" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R111" t="n">
-        <v>25</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -7606,7 +6328,7 @@
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>28_05_2017</t>
+          <t>28-05-2017</t>
         </is>
       </c>
       <c r="B7" s="29" t="n">
